--- a/01_Basic Model/02_Input Data/01_Historical/TX_Input_yearly.xlsx
+++ b/01_Basic Model/02_Input Data/01_Historical/TX_Input_yearly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fröhlich\Final\TX\1 Historical\2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Competitiveness_of_RES\01_Basic Model\02_Input Data\01_Historical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8F23EC-FC6E-423B-AAB9-5FF5C44BF92F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E6B9CC-4A79-4CD6-B160-9AAC96C0B150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{9BA085BD-A4BD-4D3B-9BBD-ABB9433EC046}"/>
+    <workbookView xWindow="38280" yWindow="45" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9BA085BD-A4BD-4D3B-9BBD-ABB9433EC046}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_conv" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -182,12 +194,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="[$-1010809]dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ &quot;DM&quot;_-;\-* #,##0.00\ &quot;DM&quot;_-;_-* &quot;-&quot;??\ &quot;DM&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.00\ _D_M_-;\-* #,##0.00\ _D_M_-;_-* &quot;-&quot;??\ _D_M_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,16 +230,461 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="72"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -231,24 +692,392 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -282,15 +1111,227 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="220">
+    <cellStyle name="20 % - Akzent1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="28" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="31" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="34" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="37" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="29" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="32" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="35" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="38" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1 2" xfId="144" xr:uid="{5C795858-07FA-45DF-90D4-9EBBB0997704}"/>
+    <cellStyle name="60 % - Akzent2 2" xfId="145" xr:uid="{7D9F41BB-8DBE-4DA6-8C3B-DC95946EB2F8}"/>
+    <cellStyle name="60 % - Akzent3 2" xfId="146" xr:uid="{699A2D2E-F76C-447B-9070-BB9287FD409D}"/>
+    <cellStyle name="60 % - Akzent4 2" xfId="147" xr:uid="{126961A9-2983-4736-B8E3-89BC0BA15D1C}"/>
+    <cellStyle name="60 % - Akzent5 2" xfId="148" xr:uid="{E7D52316-CAAF-4575-AC8B-960470601080}"/>
+    <cellStyle name="60 % - Akzent6 2" xfId="149" xr:uid="{6BD1395D-55D3-440B-83CA-F6C5AA4BAC38}"/>
+    <cellStyle name="Akzent1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="27" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="30" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="33" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="36" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="16" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="17" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Comma 11" xfId="123" xr:uid="{6FA890AE-3812-4344-B6C4-881A9491E059}"/>
+    <cellStyle name="Comma 11 2" xfId="197" xr:uid="{97AEA0F2-1DDC-4C9F-8354-48386FB97222}"/>
+    <cellStyle name="Comma 2" xfId="47" xr:uid="{455B8386-E628-453E-8912-035627D2DA7F}"/>
+    <cellStyle name="Comma 2 10" xfId="178" xr:uid="{2D794FD0-6723-4BEB-8F6F-40ABBEA44505}"/>
+    <cellStyle name="Comma 2 2" xfId="48" xr:uid="{A555D1DC-529A-4E77-8059-8BE036628FBE}"/>
+    <cellStyle name="Comma 2 2 2" xfId="179" xr:uid="{2EB573DB-71B3-4EE2-A1AE-65D59E15C89A}"/>
+    <cellStyle name="Comma 2 3" xfId="49" xr:uid="{100FB817-2898-4E8B-A14E-9D6F96B4A046}"/>
+    <cellStyle name="Comma 2 3 2" xfId="50" xr:uid="{C4C1A8C4-F12B-4616-94DB-583AA8AAE369}"/>
+    <cellStyle name="Comma 2 3 2 2" xfId="181" xr:uid="{DB0B764F-229F-4AB7-8C41-2508C7C17DEE}"/>
+    <cellStyle name="Comma 2 3 3" xfId="180" xr:uid="{673BA8CE-7226-4081-8ECB-1965BBF51A79}"/>
+    <cellStyle name="Comma 2 4" xfId="51" xr:uid="{FFCD458A-9DFD-46C8-985D-ED8368F72C5C}"/>
+    <cellStyle name="Comma 2 4 2" xfId="182" xr:uid="{6056CDCE-5E88-457C-BF8E-CC0C899F9D20}"/>
+    <cellStyle name="Comma 2 5" xfId="52" xr:uid="{E7D0F668-8246-45E6-8758-07764FFFCC53}"/>
+    <cellStyle name="Comma 2 5 2" xfId="183" xr:uid="{29694841-86BA-46F1-BA1D-A0CA1B0FF227}"/>
+    <cellStyle name="Comma 2 6" xfId="53" xr:uid="{36F7A306-901A-4079-BBC7-19C46BE37C89}"/>
+    <cellStyle name="Comma 2 6 2" xfId="184" xr:uid="{B3F6F93A-56B7-44C0-9F6A-BE432304DF42}"/>
+    <cellStyle name="Comma 2 7" xfId="54" xr:uid="{405DC28B-9A87-45BB-BF64-759CEF7E0A7D}"/>
+    <cellStyle name="Comma 2 7 2" xfId="185" xr:uid="{8B9C2E35-35BF-4F1C-B72E-0408FDEA28F1}"/>
+    <cellStyle name="Comma 2 8" xfId="55" xr:uid="{8D7F2223-DF1A-49E8-A455-D0AB9088F59C}"/>
+    <cellStyle name="Comma 2 8 2" xfId="186" xr:uid="{F99B8985-E84F-4F83-9332-0770774D43E7}"/>
+    <cellStyle name="Comma 2 9" xfId="56" xr:uid="{361C8F9E-9B40-4403-9B72-8021DD3F0DB9}"/>
+    <cellStyle name="Comma 2 9 2" xfId="187" xr:uid="{FF53AA27-E96C-4948-B962-EB778500F0DC}"/>
+    <cellStyle name="Comma 3" xfId="57" xr:uid="{D3DD8898-8E5A-4710-A04C-5B632D21909E}"/>
+    <cellStyle name="Comma 3 2" xfId="58" xr:uid="{3FDBCB4C-28B4-43CF-A391-475541C5CC59}"/>
+    <cellStyle name="Comma 3 2 2" xfId="189" xr:uid="{4F67F448-D0C9-488A-9964-C83B4C42A107}"/>
+    <cellStyle name="Comma 3 3" xfId="188" xr:uid="{A9A7EF51-2FE8-4BAA-8F1D-C8001172523C}"/>
+    <cellStyle name="Comma 4" xfId="59" xr:uid="{955103AB-19D5-4787-B80F-9DB349C47181}"/>
+    <cellStyle name="Comma 4 2" xfId="60" xr:uid="{0F98BF19-9917-4916-B40B-44F8FE668BA6}"/>
+    <cellStyle name="Comma 4 2 2" xfId="168" xr:uid="{6D5F3BB2-0552-4467-9678-D4BF79A213E5}"/>
+    <cellStyle name="Comma 4 2 2 2" xfId="215" xr:uid="{3E3E27AC-BED3-4F74-9433-D9756D3C69FA}"/>
+    <cellStyle name="Comma 4 2 3" xfId="204" xr:uid="{1D37163B-6365-434D-A345-3B9CDC50AD20}"/>
+    <cellStyle name="Comma 4 3" xfId="167" xr:uid="{5FB9ED0C-90FE-43F4-8707-548A6E3F721D}"/>
+    <cellStyle name="Comma 4 3 2" xfId="214" xr:uid="{8D11A58B-36E0-4434-8376-F04F31F6A4C9}"/>
+    <cellStyle name="Comma 4 4" xfId="203" xr:uid="{62B3438D-8C1D-4590-AF98-84CD6D9F61C0}"/>
+    <cellStyle name="Comma 5" xfId="61" xr:uid="{311D6DA8-F64C-4E01-9C08-11E4FE693CB9}"/>
+    <cellStyle name="Comma 5 2" xfId="62" xr:uid="{5BFA3899-94E8-4016-B28A-BEF703D58B62}"/>
+    <cellStyle name="Comma 5 2 2" xfId="191" xr:uid="{5C14CFAE-BFBC-47D8-8D5D-7F20155AE97F}"/>
+    <cellStyle name="Comma 5 3" xfId="190" xr:uid="{5B4B10B1-C33A-4CD7-89FB-1613EB5D35B8}"/>
+    <cellStyle name="Comma 6" xfId="63" xr:uid="{55EE107C-24D5-4C00-86E7-E56ED9224051}"/>
+    <cellStyle name="Comma 6 2" xfId="64" xr:uid="{11872A89-0F13-49DB-8934-8EEAE93A8F5F}"/>
+    <cellStyle name="Comma 6 2 2" xfId="193" xr:uid="{E784A0A1-5669-4F88-9694-27BBDF95DABE}"/>
+    <cellStyle name="Comma 6 3" xfId="65" xr:uid="{9969987F-3837-4BC9-9D2D-6774C4521C6F}"/>
+    <cellStyle name="Comma 6 3 2" xfId="194" xr:uid="{2B3E7C12-14FF-4754-A4A1-DD5A36D96317}"/>
+    <cellStyle name="Comma 6 4" xfId="192" xr:uid="{05A78809-9D60-40C2-A21B-F1FD456AAEF6}"/>
+    <cellStyle name="Comma 7" xfId="66" xr:uid="{93D84C3E-E362-4B4B-ABE2-30D46670CD16}"/>
+    <cellStyle name="Comma 7 2" xfId="195" xr:uid="{EFADD24C-9808-466C-AF49-6EAF40256B88}"/>
+    <cellStyle name="Comma 8" xfId="67" xr:uid="{2B8ABA8B-E853-425B-920C-766DE63B0AE2}"/>
+    <cellStyle name="Comma 8 2" xfId="196" xr:uid="{32FD3890-0652-46F2-B3F1-1C0729B50B25}"/>
+    <cellStyle name="Eingabe" xfId="15" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="22" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good 2" xfId="68" xr:uid="{EEAB0662-BFA2-4B90-AB14-598EFA22379B}"/>
+    <cellStyle name="Gut" xfId="13" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1 2" xfId="69" xr:uid="{0E0F49F4-C421-4D12-90A2-34D78142CFDD}"/>
+    <cellStyle name="Heading 2 2" xfId="70" xr:uid="{932EC31A-5E1C-47D9-AB2B-837C3917BB48}"/>
+    <cellStyle name="Hyperlink 2" xfId="72" xr:uid="{AC10F264-15A1-4A0D-803B-2BB36E575150}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="130" xr:uid="{73F77E43-DB00-4762-B43F-A14498D69A63}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="122" xr:uid="{421225FE-545A-476C-B1EE-CC6BB68D16AD}"/>
+    <cellStyle name="Hyperlink 2 3 2" xfId="124" xr:uid="{BA2D97D3-25D1-44A2-B0EA-9A2D3E2A2FB0}"/>
+    <cellStyle name="Hyperlink 3" xfId="73" xr:uid="{4C81C931-8384-4210-ACD5-55E51D9604A0}"/>
     <cellStyle name="Komma 2" xfId="2" xr:uid="{AF1FA308-5BB0-4765-9052-001723E4E16E}"/>
     <cellStyle name="Komma 2 2" xfId="6" xr:uid="{546B1FA4-ED3D-4CCF-BFB1-6934F261636D}"/>
     <cellStyle name="Komma 2 2 2" xfId="7" xr:uid="{C0449768-2484-446A-AB6E-F20247C009BA}"/>
+    <cellStyle name="Komma 2 2 2 2" xfId="44" xr:uid="{BA0A4372-9856-4541-8725-C0B4889E10C4}"/>
+    <cellStyle name="Komma 2 2 2 2 2" xfId="140" xr:uid="{07367F18-5089-4C37-84D5-7BE34585405E}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2" xfId="172" xr:uid="{E5FCCA24-0A20-40B1-B105-65DF2E18ADB7}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2 2" xfId="219" xr:uid="{3BA29980-9647-41E4-AC87-F9AEE1C6EF06}"/>
+    <cellStyle name="Komma 2 2 2 2 2 3" xfId="208" xr:uid="{312D165B-3D23-4759-98E4-2BF2687B993C}"/>
+    <cellStyle name="Komma 2 2 2 2 3" xfId="166" xr:uid="{256DAFA8-9816-47CB-BE10-9C7B8736421A}"/>
+    <cellStyle name="Komma 2 2 2 2 3 2" xfId="213" xr:uid="{BF2C3699-BA0A-4EE9-9FD3-8C875F51C57A}"/>
+    <cellStyle name="Komma 2 2 2 2 4" xfId="202" xr:uid="{53A4EAE8-830C-4C4C-9FCD-A4846967A926}"/>
+    <cellStyle name="Komma 2 2 2 3" xfId="138" xr:uid="{F0696719-2575-4F89-83A5-89AE094059D9}"/>
+    <cellStyle name="Komma 2 2 2 3 2" xfId="170" xr:uid="{AF7C305C-BA1F-43E9-9073-A24D6472B2E0}"/>
+    <cellStyle name="Komma 2 2 2 3 2 2" xfId="217" xr:uid="{A7AB46F8-5C76-4224-B9CC-732574195968}"/>
+    <cellStyle name="Komma 2 2 2 3 3" xfId="206" xr:uid="{1071A7F6-4C8A-4986-93D9-7CB33F210C00}"/>
+    <cellStyle name="Komma 2 2 2 4" xfId="164" xr:uid="{F2C7E12A-56E7-486D-A01A-FAD8243A85EE}"/>
+    <cellStyle name="Komma 2 2 2 4 2" xfId="211" xr:uid="{D6B6B435-369C-4D10-9EC1-C950C202E79E}"/>
+    <cellStyle name="Komma 2 2 2 5" xfId="200" xr:uid="{4E5EC380-C878-4240-9DD6-C814D89EAA7A}"/>
+    <cellStyle name="Komma 2 2 3" xfId="151" xr:uid="{5011980F-61B4-4635-AC48-68339806DDDD}"/>
+    <cellStyle name="Komma 2 2 3 2" xfId="176" xr:uid="{B0C83085-695D-4447-90E4-CB5C60A6FA93}"/>
+    <cellStyle name="Komma 2 2 4" xfId="42" xr:uid="{BCD1D4F0-E709-4230-A1D8-3936ACCD15B4}"/>
+    <cellStyle name="Komma 2 3" xfId="43" xr:uid="{3F23E854-F1A9-46C2-AEFC-8987651C6408}"/>
+    <cellStyle name="Komma 2 3 2" xfId="139" xr:uid="{8A54716A-0B84-4A80-89F4-B41DFB13A1FB}"/>
+    <cellStyle name="Komma 2 3 2 2" xfId="171" xr:uid="{5D10E1A8-DB3C-4F39-B113-A0867B20D447}"/>
+    <cellStyle name="Komma 2 3 2 2 2" xfId="218" xr:uid="{73A9A43A-9255-432A-A488-652DFF5B0723}"/>
+    <cellStyle name="Komma 2 3 2 3" xfId="207" xr:uid="{8A83CF66-72B8-4673-9231-EF4078DEB816}"/>
+    <cellStyle name="Komma 2 3 3" xfId="152" xr:uid="{6AB66DA5-F9A5-4430-A860-22208C8785CB}"/>
+    <cellStyle name="Komma 2 3 4" xfId="165" xr:uid="{4AA7364A-8402-466B-A9EF-A58FE9638191}"/>
+    <cellStyle name="Komma 2 3 4 2" xfId="212" xr:uid="{33213653-E8DB-466C-9AE7-535DC1A42558}"/>
+    <cellStyle name="Komma 2 3 5" xfId="201" xr:uid="{8ACF065C-99E1-4BC0-88A0-D466411B71C5}"/>
+    <cellStyle name="Komma 2 4" xfId="136" xr:uid="{2D4FB7C5-C029-4D39-90AF-54D8B31E838E}"/>
+    <cellStyle name="Komma 2 4 2" xfId="169" xr:uid="{B1791884-174B-4B02-BC7E-F3B687FB5082}"/>
+    <cellStyle name="Komma 2 4 2 2" xfId="216" xr:uid="{4D289944-0CDE-49B4-84F4-EF957D2AE408}"/>
+    <cellStyle name="Komma 2 4 3" xfId="205" xr:uid="{DBF711F6-A9CA-4230-A37C-7704A9D52C39}"/>
+    <cellStyle name="Komma 2 5" xfId="142" xr:uid="{D396A26E-646A-45C8-B484-57859CFA6785}"/>
+    <cellStyle name="Komma 2 6" xfId="163" xr:uid="{B1821ACD-34D3-4353-A83C-AFAAD5729BAE}"/>
+    <cellStyle name="Komma 2 6 2" xfId="210" xr:uid="{72256F4F-7FC5-4F05-8ED0-CC2D9D8D791E}"/>
+    <cellStyle name="Komma 2 7" xfId="199" xr:uid="{3D348113-4916-4B56-B173-B8B44F904A5E}"/>
+    <cellStyle name="Komma 3" xfId="46" xr:uid="{374C22A1-4A78-4E73-905E-556136D79EFC}"/>
+    <cellStyle name="Komma 3 2" xfId="150" xr:uid="{69B6F918-5084-4188-87EC-07CED0B15015}"/>
+    <cellStyle name="Komma 3 2 2" xfId="177" xr:uid="{21602A85-730A-4D50-950F-C65C478CBFD0}"/>
+    <cellStyle name="Komma 4" xfId="134" xr:uid="{BCF3D22E-C08E-42C6-8F76-4005F56434C8}"/>
+    <cellStyle name="Komma 4 2" xfId="154" xr:uid="{3805F783-E8C2-45F9-9EAC-DD3076029B4A}"/>
+    <cellStyle name="Komma 4 2 2" xfId="198" xr:uid="{2F766FA0-185F-4089-A3D4-34931465B7B7}"/>
+    <cellStyle name="Komma 4 2 3" xfId="209" xr:uid="{1D14A8AD-477D-4994-BDFC-A63E6D864D73}"/>
+    <cellStyle name="Komma 5" xfId="156" xr:uid="{0A4A8E27-0020-4462-80A2-0B3BA9C9213B}"/>
+    <cellStyle name="Link 2" xfId="71" xr:uid="{299DC7E1-DD4F-4B30-9627-2D88672C4164}"/>
+    <cellStyle name="Link 2 2" xfId="157" xr:uid="{382FD6C5-A96A-4A1E-B6A3-8934FB11131B}"/>
+    <cellStyle name="Neutral 2" xfId="143" xr:uid="{53822DF5-89AC-4F52-AF09-FABB57846C0F}"/>
+    <cellStyle name="Normal 10" xfId="74" xr:uid="{119CAE1B-78D5-4556-A694-D56502BB5161}"/>
+    <cellStyle name="Normal 11" xfId="75" xr:uid="{D6CB0161-081A-425E-9245-63D40A3BF7B0}"/>
+    <cellStyle name="Normal 12" xfId="76" xr:uid="{22B8F61D-14D8-4651-863D-7CF77B2B22FB}"/>
+    <cellStyle name="Normal 13" xfId="77" xr:uid="{68DB7812-11E2-4B76-8D22-BF59ACEFB4DB}"/>
+    <cellStyle name="Normal 14" xfId="78" xr:uid="{DFC77FBE-A524-427B-A249-F1F3E7E89225}"/>
+    <cellStyle name="Normal 15" xfId="79" xr:uid="{673E1E76-FF58-4383-A142-1C4F2203EDD7}"/>
+    <cellStyle name="Normal 16" xfId="80" xr:uid="{5633239B-7D3A-4F23-954C-3C973B17C68D}"/>
+    <cellStyle name="Normal 17" xfId="81" xr:uid="{073B1F69-425C-40BD-8D47-0DC6DA3110D5}"/>
+    <cellStyle name="Normal 17 2" xfId="82" xr:uid="{52C48550-8947-4DA9-9B58-DFFA74339E31}"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{098744FE-9844-4518-A91E-00A8F4258A86}"/>
     <cellStyle name="Normal 2 2" xfId="5" xr:uid="{FCD300CD-8039-44DF-B12D-F1531F7C3F26}"/>
+    <cellStyle name="Normal 2 2 2" xfId="84" xr:uid="{2564EA86-050F-4ED1-B637-22A222AA58B4}"/>
+    <cellStyle name="Normal 2 3" xfId="85" xr:uid="{E8D62709-C031-4A03-AAB4-CCBCFFEF8357}"/>
+    <cellStyle name="Normal 2 4" xfId="86" xr:uid="{482DF4EA-23DE-44CB-AB02-78F8F1C17B37}"/>
+    <cellStyle name="Normal 2 5" xfId="83" xr:uid="{26363178-F882-4968-96DF-A23FE3C80B67}"/>
+    <cellStyle name="Normal 2 6" xfId="129" xr:uid="{AA4B25E9-4FC8-44E7-9D4C-EB34550C2D33}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{FA51F745-E432-4830-B289-30C69457E580}"/>
+    <cellStyle name="Normal 3 2" xfId="88" xr:uid="{7A8D92C3-0CC6-416A-A899-C7B4B18DF8BC}"/>
+    <cellStyle name="Normal 3 2 2" xfId="89" xr:uid="{E134F057-E0DC-4C73-9769-AF9C039A1E87}"/>
+    <cellStyle name="Normal 3 3" xfId="90" xr:uid="{E9BB9858-2050-44D3-A958-DA46F90039BA}"/>
+    <cellStyle name="Normal 3 4" xfId="91" xr:uid="{121BE0C7-7084-49D1-ABF2-C3AD06C23595}"/>
+    <cellStyle name="Normal 3 5" xfId="87" xr:uid="{FCE01C2F-CCB5-43FC-A4F5-85E5C60F21A7}"/>
+    <cellStyle name="Normal 4" xfId="92" xr:uid="{26302295-9548-42F6-B7DC-95B64369C14D}"/>
+    <cellStyle name="Normal 4 2" xfId="93" xr:uid="{B1AD8B2F-D3FA-4D2E-B775-B3D9D46F4B60}"/>
+    <cellStyle name="Normal 4 2 2" xfId="94" xr:uid="{44261DF1-F81D-4A3D-A894-E527AE2A2D4F}"/>
+    <cellStyle name="Normal 4 3" xfId="95" xr:uid="{C5CEBCD5-481C-4053-8707-CC6AB6612C7D}"/>
+    <cellStyle name="Normal 4 3 2" xfId="127" xr:uid="{376FE887-3E15-41CE-ACA7-16B78E3E3BE1}"/>
+    <cellStyle name="Normal 4 4" xfId="96" xr:uid="{F0387983-1093-4B6E-B150-1DA89B358FCB}"/>
+    <cellStyle name="Normal 4 5" xfId="128" xr:uid="{F1CE2282-0C33-46DA-90B3-7552785A34B0}"/>
+    <cellStyle name="Normal 5" xfId="97" xr:uid="{D9DEA4C9-C93B-49D8-81BB-196A2F6E854B}"/>
+    <cellStyle name="Normal 5 2" xfId="98" xr:uid="{ADE03E28-7DD0-4FCD-A1F9-D0396C1A6221}"/>
+    <cellStyle name="Normal 6" xfId="99" xr:uid="{EFED4165-E5C1-4031-BCE7-65B5F16DCD3B}"/>
+    <cellStyle name="Normal 6 2" xfId="100" xr:uid="{17D65241-E185-404A-A43C-C334254E5249}"/>
+    <cellStyle name="Normal 7" xfId="101" xr:uid="{F6FBE71B-7EDF-40F0-A160-44D4339FC8CC}"/>
+    <cellStyle name="Normal 7 2" xfId="102" xr:uid="{D3A22C14-E0C9-43D5-97AC-2A7065623A56}"/>
+    <cellStyle name="Normal 8" xfId="103" xr:uid="{C02A2DFE-45A3-48F1-A24B-D9086506C41C}"/>
+    <cellStyle name="Normal 8 2" xfId="104" xr:uid="{7F33EC9D-DA31-4A31-B753-E4CDFFC82FBF}"/>
+    <cellStyle name="Normal 8 3" xfId="105" xr:uid="{129A19E3-AC3D-4831-96C6-8118522BEBB9}"/>
+    <cellStyle name="Normal 8 4" xfId="106" xr:uid="{02F73A37-9651-443A-B261-715E4D281431}"/>
+    <cellStyle name="Normal 8 5" xfId="126" xr:uid="{3A4176FA-B51D-474A-8135-A31D906D2183}"/>
+    <cellStyle name="Normal 9" xfId="107" xr:uid="{7B34B00C-C729-4110-AF63-CFF0D35C0FA4}"/>
+    <cellStyle name="Normal 9 2" xfId="108" xr:uid="{C147F2C3-F00F-4B41-8C97-159F2450F8EE}"/>
+    <cellStyle name="Normal 9 3" xfId="109" xr:uid="{80DE39F9-A519-4CCB-B80A-85EE3F8D138C}"/>
+    <cellStyle name="Notiz" xfId="21" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Notiz 2" xfId="162" xr:uid="{890D3FE0-93C1-49E9-976E-7BED01961448}"/>
+    <cellStyle name="Percent 2" xfId="111" xr:uid="{B63544DD-3541-4E50-9DAD-E532D5FC4D18}"/>
+    <cellStyle name="Percent 3" xfId="112" xr:uid="{65277ABD-9672-45DA-BC54-01C0B9C01D39}"/>
+    <cellStyle name="Percent 3 2" xfId="113" xr:uid="{06253166-719B-4284-A28E-900A1E006088}"/>
+    <cellStyle name="Percent 4" xfId="114" xr:uid="{11B64FE7-483C-49E0-A5D9-8DD82412DAA7}"/>
+    <cellStyle name="Percent 4 2" xfId="115" xr:uid="{055268DC-F0ED-480E-94F0-93EB680B4F38}"/>
+    <cellStyle name="Percent 5" xfId="116" xr:uid="{A5407EF8-83C2-40D4-9F59-92EB5C5C9A8A}"/>
+    <cellStyle name="Percent 5 2" xfId="117" xr:uid="{87E9D57E-F758-4B92-B684-E6461C2E2B1B}"/>
+    <cellStyle name="Percent 6" xfId="118" xr:uid="{6FD12483-AD04-488F-8CAD-E89A9D43EE40}"/>
+    <cellStyle name="Percent 6 2" xfId="119" xr:uid="{C08F937B-34D5-4F3D-BEA2-324FE703CEF3}"/>
+    <cellStyle name="Percent 6 3" xfId="120" xr:uid="{0FB7F643-DE40-4C5E-BA18-3CF5112812D1}"/>
+    <cellStyle name="Percent 7" xfId="121" xr:uid="{12ABF678-7BC8-42D5-A2FA-8329239568A6}"/>
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent 2" xfId="110" xr:uid="{C27922B8-44CE-4991-87F9-3F006C19CCB9}"/>
+    <cellStyle name="Prozent 3" xfId="125" xr:uid="{27F26A65-2C68-48A2-B81B-AD52CF5A15B1}"/>
+    <cellStyle name="Schlecht" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="45" xr:uid="{C498EA8C-8F6E-49AE-8622-D1A6BE92741A}"/>
+    <cellStyle name="Standard 2 2" xfId="161" xr:uid="{A60C47CF-EC4D-46F6-8703-814FD286AE98}"/>
+    <cellStyle name="Standard 2 2 2" xfId="174" xr:uid="{A153967D-2539-47D2-9053-EBCF8A4AE11C}"/>
+    <cellStyle name="Standard 2 3" xfId="158" xr:uid="{468D0A3D-1D2E-4974-8842-2E1F48F531FF}"/>
+    <cellStyle name="Standard 2 4" xfId="141" xr:uid="{D628C09D-EE03-466B-A902-29A2D0D7B618}"/>
+    <cellStyle name="Standard 3" xfId="135" xr:uid="{C524EC7F-50CC-4BE7-B93E-2505FD50ED3B}"/>
+    <cellStyle name="Standard 3 2" xfId="160" xr:uid="{96A91A37-F4DF-4B67-9F8D-965071D2FA7D}"/>
+    <cellStyle name="Standard 3 2 2" xfId="175" xr:uid="{563F3478-FBDC-4933-96CB-FCB5CA0C2F4E}"/>
+    <cellStyle name="Standard 4" xfId="137" xr:uid="{6A6A5E43-4C58-4ED3-9BEB-BF52E568D16C}"/>
+    <cellStyle name="Standard 4 2" xfId="155" xr:uid="{DFD2EC31-8B8D-4501-82AB-3DA207955ADD}"/>
+    <cellStyle name="Standard 5" xfId="173" xr:uid="{AE2CB507-32AF-4459-9D40-9C5CEFDF443D}"/>
+    <cellStyle name="Überschrift" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1 2" xfId="133" xr:uid="{1CA88420-63AF-4A90-AF07-F0B15B7A035C}"/>
+    <cellStyle name="Überschrift 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2 2" xfId="132" xr:uid="{79A59D2F-FCED-4ED4-A561-70C5BB321A0B}"/>
+    <cellStyle name="Überschrift 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3 2" xfId="131" xr:uid="{92B8EB58-577F-4A5F-B7F6-435667E7119E}"/>
+    <cellStyle name="Überschrift 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Überschrift 5" xfId="153" xr:uid="{65BA621B-3869-4C4F-9A98-BA545908C5E3}"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="18" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Währung 2" xfId="159" xr:uid="{BCC65902-7F59-4410-A894-77E02E02F364}"/>
+    <cellStyle name="Warnender Text" xfId="20" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="19" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1088,8 +2129,8 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1114,8 +2155,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1140,8 +2181,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1166,8 +2207,8 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1192,8 +2233,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1218,8 +2259,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1244,8 +2285,8 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1270,8 +2311,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>0</v>
+      <c r="F12" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1296,8 +2337,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>0</v>
+      <c r="F13" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1322,8 +2363,8 @@
       <c r="E14" s="13">
         <v>0</v>
       </c>
-      <c r="F14" s="13">
-        <v>0</v>
+      <c r="F14" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
